--- a/i18n/strings-th.xlsx
+++ b/i18n/strings-th.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C145"/>
+  <dimension ref="A1:C146"/>
   <cols>
     <col min="1" max="1" width="18.83203125" customWidth="1"/>
     <col min="2" max="2" width="64.83203125" customWidth="1"/>
@@ -1999,9 +1999,20 @@
         <v>เพิ่มพลังโจมตี 7 วินาที</v>
       </c>
     </row>
+    <row r="146">
+      <c r="A146" t="str">
+        <v>K-푸드 사격</v>
+      </c>
+      <c r="B146" t="str">
+        <v>이동 속도</v>
+      </c>
+      <c r="C146" t="str">
+        <v>ความเร็วเคลื่อนที่</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C145"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C146"/>
   </ignoredErrors>
 </worksheet>
 </file>